--- a/results/MH-urban5.xlsx
+++ b/results/MH-urban5.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alessiosclafani/Desktop/PhD/crawford/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D2A520-EFE0-954F-8533-3525FEED91DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97983EF-083C-4A48-B165-872D845A0095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28040" windowHeight="17060" activeTab="2" xr2:uid="{074F7990-151F-2D45-8994-98A44BBB97C2}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28040" windowHeight="17060" xr2:uid="{074F7990-151F-2D45-8994-98A44BBB97C2}"/>
   </bookViews>
   <sheets>
     <sheet name="MH-roma5" sheetId="4" r:id="rId1"/>
     <sheet name="MH-napoli5" sheetId="3" r:id="rId2"/>
     <sheet name="MH-milano5" sheetId="1" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="174">
   <si>
     <t>N.H. o-d</t>
   </si>
@@ -557,13 +560,23 @@
   </si>
   <si>
     <t>MILANO-50-5-nc</t>
+  </si>
+  <si>
+    <t>GAP-MM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -589,15 +602,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Percentuale" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -610,6 +627,929 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="MM-roma5"/>
+      <sheetName val="MM-napoli5"/>
+      <sheetName val="MM-milano5"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="S2">
+            <v>14.0116393378949</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="S3">
+            <v>13.2519321021894</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="S4">
+            <v>9.4684939676164692</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="S5">
+            <v>8.4207899670721407</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="S6">
+            <v>13.021038220526499</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="S7">
+            <v>13.0018244171813</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="S8">
+            <v>10.948531278160701</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="S9">
+            <v>7.0885352245955202</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="S10">
+            <v>6.5929822595916203</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="S11">
+            <v>9.7350650267323005</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="S12">
+            <v>18.384401701466999</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="S13">
+            <v>18.420736431439899</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="S14">
+            <v>32.120677785006897</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="S15">
+            <v>18.618623334082798</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="S16">
+            <v>25.869340638354199</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="S17">
+            <v>25.3895790155564</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="S18">
+            <v>20.220438934522399</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="S19">
+            <v>29.149228041303001</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="S20">
+            <v>24.136609094884399</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="S21">
+            <v>23.385736204396999</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="S22">
+            <v>34.0050005331249</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="S23">
+            <v>43.338289367497701</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="S24">
+            <v>25.536833953888902</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="S25">
+            <v>35.741945260230501</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="S26">
+            <v>36.420871516475799</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="S27">
+            <v>35.0345546692919</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="S28">
+            <v>37.114686834597698</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="S29">
+            <v>35.652133408131697</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="S30">
+            <v>38.346424301624097</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="S31">
+            <v>34.178202019030302</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="S32">
+            <v>55.166126688926198</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="S33">
+            <v>48.316938586479402</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="S34">
+            <v>40.962540561998303</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="S35">
+            <v>42.870411943813899</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="S36">
+            <v>38.195181091642397</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="S37">
+            <v>46.334736795900099</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="S38">
+            <v>46.917507657479597</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="S39">
+            <v>35.845019127102901</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="S40">
+            <v>46.003883159006598</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="S41">
+            <v>49.967937097539298</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="S42">
+            <v>60.453513568892099</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="S43">
+            <v>67.694211186069495</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="S44">
+            <v>64.258363530394504</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="S45">
+            <v>59.804840922733199</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="S46">
+            <v>63.397345756324</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="S47">
+            <v>63.033771797798998</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="S48">
+            <v>64.180183753846407</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="S49">
+            <v>59.510565189664099</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="S50">
+            <v>60.385712594362303</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="S51">
+            <v>66.066139663268999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="S2">
+            <v>14.3490194132602</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="S3">
+            <v>8.1845214300659599</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="S4">
+            <v>6.3762983166081399</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="S5">
+            <v>6.1228968146935996</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="S6">
+            <v>11.8335770772805</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="S7">
+            <v>11.5563138364442</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="S8">
+            <v>13.3100256070644</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="S9">
+            <v>10.3845350143391</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="S10">
+            <v>8.1944445910219308</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="S11">
+            <v>9.3128370665481004</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="S12">
+            <v>17.7255576921653</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="S13">
+            <v>23.223030025505299</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="S14">
+            <v>21.883621559940298</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="S15">
+            <v>23.43533925393</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="S16">
+            <v>22.3571867937866</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="S17">
+            <v>19.243079210271201</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="S18">
+            <v>21.419621230922999</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="S19">
+            <v>22.162198908187801</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="S20">
+            <v>20.979596911132901</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="S21">
+            <v>22.218812096368801</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="S22">
+            <v>24.170958900429302</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="S23">
+            <v>28.174115038064599</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="S24">
+            <v>28.785920280754102</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="S25">
+            <v>42.354737273464401</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="S26">
+            <v>30.668838719957101</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="S27">
+            <v>21.7491655134518</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="S28">
+            <v>30.043915146355499</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="S29">
+            <v>39.1659886233858</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="S30">
+            <v>36.072375318939301</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="S31">
+            <v>29.3249322828351</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="S32">
+            <v>33.4651381074003</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="S33">
+            <v>45.726008790425603</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="S34">
+            <v>34.744323996596101</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="S35">
+            <v>42.393048266850798</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="S36">
+            <v>37.310520820975597</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="S37">
+            <v>34.648496910041999</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="S38">
+            <v>39.012260954671298</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="S39">
+            <v>29.787682163917101</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="S40">
+            <v>38.3377909130257</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="S41">
+            <v>42.140421313407401</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="S42">
+            <v>40.9176513691704</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="S43">
+            <v>43.5856472760941</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="S44">
+            <v>54.704813686601902</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="S45">
+            <v>51.555063488425802</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="S46">
+            <v>61.221461321562401</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="S47">
+            <v>48.7368849048732</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="S48">
+            <v>45.675368236826102</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="S49">
+            <v>51.655480989081703</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="S50">
+            <v>49.3757628872429</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="S51">
+            <v>49.670916540677503</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="S2">
+            <v>12.083785621642599</v>
+          </cell>
+          <cell r="U2">
+            <v>12.083785621642599</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="S3">
+            <v>17.143345555100598</v>
+          </cell>
+          <cell r="U3">
+            <v>17.143345555100598</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="S4">
+            <v>9.6810900661572106</v>
+          </cell>
+          <cell r="U4">
+            <v>9.6810900661572106</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="S5">
+            <v>12.4094630110907</v>
+          </cell>
+          <cell r="U5">
+            <v>12.4094630110907</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="S6">
+            <v>12.047781394951199</v>
+          </cell>
+          <cell r="U6">
+            <v>12.047781394951199</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="S7">
+            <v>9.3230113493137399</v>
+          </cell>
+          <cell r="U7">
+            <v>9.3230113493137399</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="S8">
+            <v>7.5010861563244404</v>
+          </cell>
+          <cell r="U8">
+            <v>7.5010861563244404</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="S9">
+            <v>10.5604950347146</v>
+          </cell>
+          <cell r="U9">
+            <v>10.5604950347146</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="S10">
+            <v>17.3824601151248</v>
+          </cell>
+          <cell r="U10">
+            <v>17.3824601151248</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="S11">
+            <v>15.0876473125918</v>
+          </cell>
+          <cell r="U11">
+            <v>15.0876473125918</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="S12">
+            <v>18.4355457317779</v>
+          </cell>
+          <cell r="U12">
+            <v>18.4355457317779</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="S13">
+            <v>23.6632212970819</v>
+          </cell>
+          <cell r="U13">
+            <v>23.6632212970819</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="S14">
+            <v>32.943420041709203</v>
+          </cell>
+          <cell r="U14">
+            <v>32.943420041709203</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="S15">
+            <v>22.794639633259902</v>
+          </cell>
+          <cell r="U15">
+            <v>22.794639633259902</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="S16">
+            <v>18.196679699128801</v>
+          </cell>
+          <cell r="U16">
+            <v>18.196679699128801</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="S17">
+            <v>18.1464971044898</v>
+          </cell>
+          <cell r="U17">
+            <v>18.1464971044898</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="S18">
+            <v>19.760804665560901</v>
+          </cell>
+          <cell r="U18">
+            <v>19.760804665560901</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="S19">
+            <v>23.6038108825623</v>
+          </cell>
+          <cell r="U19">
+            <v>23.6038108825623</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="S20">
+            <v>22.852053700559001</v>
+          </cell>
+          <cell r="U20">
+            <v>22.852053700559001</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="S21">
+            <v>27.5886923837915</v>
+          </cell>
+          <cell r="U21">
+            <v>27.5886923837914</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="S22">
+            <v>36.355978565502397</v>
+          </cell>
+          <cell r="U22">
+            <v>36.355978565502397</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="S23">
+            <v>41.941696866512501</v>
+          </cell>
+          <cell r="U23">
+            <v>41.941696866512501</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="S24">
+            <v>37.836353167124003</v>
+          </cell>
+          <cell r="U24">
+            <v>37.836353167124003</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="S25">
+            <v>39.179539171813197</v>
+          </cell>
+          <cell r="U25">
+            <v>39.179539171813197</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="S26">
+            <v>28.637649902619899</v>
+          </cell>
+          <cell r="U26">
+            <v>28.637649902619899</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="S27">
+            <v>31.187111837703998</v>
+          </cell>
+          <cell r="U27">
+            <v>31.187111837703998</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="S28">
+            <v>33.904752112670799</v>
+          </cell>
+          <cell r="U28">
+            <v>33.904752112670799</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="S29">
+            <v>51.474823212449998</v>
+          </cell>
+          <cell r="U29">
+            <v>51.474823212449998</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="S30">
+            <v>34.348114150707303</v>
+          </cell>
+          <cell r="U30">
+            <v>34.348114150707303</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="S31">
+            <v>42.583800030746403</v>
+          </cell>
+          <cell r="U31">
+            <v>42.583800030746403</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="S32">
+            <v>46.397465323985998</v>
+          </cell>
+          <cell r="U32">
+            <v>46.397465323985998</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="S33">
+            <v>48.373571549456102</v>
+          </cell>
+          <cell r="U33">
+            <v>48.373571549456102</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="S34">
+            <v>50.860022967645698</v>
+          </cell>
+          <cell r="U34">
+            <v>50.860022967645698</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="S35">
+            <v>37.174171698462402</v>
+          </cell>
+          <cell r="U35">
+            <v>37.174171698462402</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="S36">
+            <v>49.922518770279403</v>
+          </cell>
+          <cell r="U36">
+            <v>49.922518770279403</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="S37">
+            <v>45.999429511537798</v>
+          </cell>
+          <cell r="U37">
+            <v>45.999429511537798</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="S38">
+            <v>53.152202672213498</v>
+          </cell>
+          <cell r="U38">
+            <v>53.152202672213498</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="S39">
+            <v>43.234620308464798</v>
+          </cell>
+          <cell r="U39">
+            <v>43.234620308464798</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="S40">
+            <v>41.4585412081234</v>
+          </cell>
+          <cell r="U40">
+            <v>41.4585412081234</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="S41">
+            <v>41.528653421660202</v>
+          </cell>
+          <cell r="U41">
+            <v>41.528653421660202</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="S42">
+            <v>46.195567330139703</v>
+          </cell>
+          <cell r="U42">
+            <v>46.195567330139703</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="S43">
+            <v>58.533857538790997</v>
+          </cell>
+          <cell r="U43">
+            <v>58.533857538790997</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="S44">
+            <v>60.2272524101462</v>
+          </cell>
+          <cell r="U44">
+            <v>60.2272524101462</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="S45">
+            <v>67.511100291182004</v>
+          </cell>
+          <cell r="U45">
+            <v>67.511100291182004</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="S46">
+            <v>68.170568689243694</v>
+          </cell>
+          <cell r="U46">
+            <v>68.170568689243694</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="S47">
+            <v>59.613596140198602</v>
+          </cell>
+          <cell r="U47">
+            <v>59.613596140198602</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="S48">
+            <v>66.975869128180193</v>
+          </cell>
+          <cell r="U48">
+            <v>66.975869128180193</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="S49">
+            <v>75.606264778819394</v>
+          </cell>
+          <cell r="U49">
+            <v>75.606264778819394</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="S50">
+            <v>58.8164965154836</v>
+          </cell>
+          <cell r="U50">
+            <v>58.8164965154836</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="S51">
+            <v>73.981243168061198</v>
+          </cell>
+          <cell r="U51">
+            <v>73.981243168061198</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -929,10 +1869,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FECA0F5-E9E4-0842-B557-7A22687BAE2C}">
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1002,8 +1942,11 @@
       <c r="X1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1076,8 +2019,12 @@
       <c r="X2">
         <v>2.5086164474487301E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y2" s="2">
+        <f>(N2-'[1]MM-roma5'!S2)/'[1]MM-roma5'!S2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1150,8 +2097,12 @@
       <c r="X3">
         <v>1.7086029052734299E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y3" s="2">
+        <f>(N3-'[1]MM-roma5'!S3)/'[1]MM-roma5'!S3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1224,8 +2175,12 @@
       <c r="X4">
         <v>1.6386032104492101E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y4" s="2">
+        <f>(N4-'[1]MM-roma5'!S4)/'[1]MM-roma5'!S4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -1298,8 +2253,12 @@
       <c r="X5">
         <v>1.3561010360717701E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y5" s="2">
+        <f>(N5-'[1]MM-roma5'!S5)/'[1]MM-roma5'!S5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1372,8 +2331,12 @@
       <c r="X6">
         <v>1.94880962371826E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y6" s="2">
+        <f>(N6-'[1]MM-roma5'!S6)/'[1]MM-roma5'!S6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1446,8 +2409,12 @@
       <c r="X7">
         <v>1.68499946594238E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2">
+        <f>(N7-'[1]MM-roma5'!S7)/'[1]MM-roma5'!S7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1520,8 +2487,12 @@
       <c r="X8">
         <v>1.8479108810424801E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="2">
+        <f>(N8-'[1]MM-roma5'!S8)/'[1]MM-roma5'!S8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1594,8 +2565,12 @@
       <c r="X9">
         <v>1.6650915145873999E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="2">
+        <f>(N9-'[1]MM-roma5'!S9)/'[1]MM-roma5'!S9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1668,8 +2643,12 @@
       <c r="X10">
         <v>1.0346889495849601E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="2">
+        <f>(N10-'[1]MM-roma5'!S10)/'[1]MM-roma5'!S10</f>
+        <v>1.481873032873373E-15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1742,8 +2721,12 @@
       <c r="X11">
         <v>1.6150951385497998E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="2">
+        <f>(N11-'[1]MM-roma5'!S11)/'[1]MM-roma5'!S11</f>
+        <v>9.123497555087762E-16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1816,8 +2799,12 @@
       <c r="X12">
         <v>2.83629894256591E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="2">
+        <f>(N12-'[1]MM-roma5'!S12)/'[1]MM-roma5'!S12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1890,8 +2877,12 @@
       <c r="X13">
         <v>2.8835058212280201E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="2">
+        <f>(N13-'[1]MM-roma5'!S13)/'[1]MM-roma5'!S13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1964,8 +2955,12 @@
       <c r="X14">
         <v>0.125914096832275</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="2">
+        <f>(N14-'[1]MM-roma5'!S14)/'[1]MM-roma5'!S14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2038,8 +3033,12 @@
       <c r="X15">
         <v>2.2439002990722601E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="2">
+        <f>(N15-'[1]MM-roma5'!S15)/'[1]MM-roma5'!S15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -2112,8 +3111,12 @@
       <c r="X16">
         <v>5.5266141891479402E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="2">
+        <f>(N16-'[1]MM-roma5'!S16)/'[1]MM-roma5'!S16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -2186,8 +3189,12 @@
       <c r="X17">
         <v>5.6864023208618102E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="2">
+        <f>(N17-'[1]MM-roma5'!S17)/'[1]MM-roma5'!S17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2260,8 +3267,12 @@
       <c r="X18">
         <v>5.5666923522949198E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="2">
+        <f>(N18-'[1]MM-roma5'!S18)/'[1]MM-roma5'!S18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -2334,8 +3345,12 @@
       <c r="X19">
         <v>6.05301856994628E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="2">
+        <f>(N19-'[1]MM-roma5'!S19)/'[1]MM-roma5'!S19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -2408,8 +3423,12 @@
       <c r="X20">
         <v>5.4704189300537102E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="2">
+        <f>(N20-'[1]MM-roma5'!S20)/'[1]MM-roma5'!S20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -2482,8 +3501,12 @@
       <c r="X21">
         <v>3.6074876785278299E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="2">
+        <f>(N21-'[1]MM-roma5'!S21)/'[1]MM-roma5'!S21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2556,8 +3579,12 @@
       <c r="X22">
         <v>0.11458396911620999</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="2">
+        <f>(N22-'[1]MM-roma5'!S22)/'[1]MM-roma5'!S22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -2630,8 +3657,12 @@
       <c r="X23">
         <v>8.44900608062744E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="2">
+        <f>(N23-'[1]MM-roma5'!S23)/'[1]MM-roma5'!S23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -2704,8 +3735,12 @@
       <c r="X24">
         <v>3.7769079208374003E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="2">
+        <f>(N24-'[1]MM-roma5'!S24)/'[1]MM-roma5'!S24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -2778,8 +3813,12 @@
       <c r="X25">
         <v>7.7831983566284096E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="2">
+        <f>(N25-'[1]MM-roma5'!S25)/'[1]MM-roma5'!S25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -2852,8 +3891,12 @@
       <c r="X26">
         <v>5.2213191986083901E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="2">
+        <f>(N26-'[1]MM-roma5'!S26)/'[1]MM-roma5'!S26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -2926,8 +3969,12 @@
       <c r="X27">
         <v>0.107384204864501</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="2">
+        <f>(N27-'[1]MM-roma5'!S27)/'[1]MM-roma5'!S27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -3000,8 +4047,12 @@
       <c r="X28">
         <v>6.7056894302368095E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="2">
+        <f>(N28-'[1]MM-roma5'!S28)/'[1]MM-roma5'!S28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -3074,8 +4125,12 @@
       <c r="X29">
         <v>7.6153039932250893E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="2">
+        <f>(N29-'[1]MM-roma5'!S29)/'[1]MM-roma5'!S29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -3148,8 +4203,12 @@
       <c r="X30">
         <v>0.103295087814331</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="2">
+        <f>(N30-'[1]MM-roma5'!S30)/'[1]MM-roma5'!S30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -3222,8 +4281,12 @@
       <c r="X31">
         <v>7.4761867523193304E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="2">
+        <f>(N31-'[1]MM-roma5'!S31)/'[1]MM-roma5'!S31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>53</v>
       </c>
@@ -3296,8 +4359,12 @@
       <c r="X32">
         <v>0.16227698326110801</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="2">
+        <f>(N32-'[1]MM-roma5'!S32)/'[1]MM-roma5'!S32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>54</v>
       </c>
@@ -3370,8 +4437,12 @@
       <c r="X33">
         <v>0.14893984794616699</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="2">
+        <f>(N33-'[1]MM-roma5'!S33)/'[1]MM-roma5'!S33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>55</v>
       </c>
@@ -3444,8 +4515,12 @@
       <c r="X34">
         <v>9.7105979919433594E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="2">
+        <f>(N34-'[1]MM-roma5'!S34)/'[1]MM-roma5'!S34</f>
+        <v>2.4284622399300036E-15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -3518,8 +4593,12 @@
       <c r="X35">
         <v>0.10648298263549801</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="2">
+        <f>(N35-'[1]MM-roma5'!S35)/'[1]MM-roma5'!S35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>57</v>
       </c>
@@ -3592,8 +4671,12 @@
       <c r="X36">
         <v>7.9424858093261705E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y36" s="2">
+        <f>(N36-'[1]MM-roma5'!S36)/'[1]MM-roma5'!S36</f>
+        <v>-2.6044118698570767E-15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>58</v>
       </c>
@@ -3666,8 +4749,12 @@
       <c r="X37">
         <v>0.17156600952148399</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y37" s="2">
+        <f>(N37-'[1]MM-roma5'!S37)/'[1]MM-roma5'!S37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>59</v>
       </c>
@@ -3740,8 +4827,12 @@
       <c r="X38">
         <v>0.17808079719543399</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2">
+        <f>(N38-'[1]MM-roma5'!S38)/'[1]MM-roma5'!S38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>60</v>
       </c>
@@ -3814,8 +4905,12 @@
       <c r="X39">
         <v>0.128787040710449</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="2">
+        <f>(N39-'[1]MM-roma5'!S39)/'[1]MM-roma5'!S39</f>
+        <v>-2.7751689196672489E-15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>61</v>
       </c>
@@ -3888,8 +4983,12 @@
       <c r="X40">
         <v>0.14154005050659099</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="2">
+        <f>(N40-'[1]MM-roma5'!S40)/'[1]MM-roma5'!S40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>62</v>
       </c>
@@ -3962,8 +5061,12 @@
       <c r="X41">
         <v>0.15793800354003901</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="2">
+        <f>(N41-'[1]MM-roma5'!S41)/'[1]MM-roma5'!S41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>63</v>
       </c>
@@ -4036,8 +5139,12 @@
       <c r="X42">
         <v>0.155776977539062</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="2">
+        <f>(N42-'[1]MM-roma5'!S42)/'[1]MM-roma5'!S42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>64</v>
       </c>
@@ -4110,8 +5217,12 @@
       <c r="X43">
         <v>0.27055382728576599</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="2">
+        <f>(N43-'[1]MM-roma5'!S43)/'[1]MM-roma5'!S43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>65</v>
       </c>
@@ -4184,8 +5295,12 @@
       <c r="X44">
         <v>0.197654008865356</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="2">
+        <f>(N44-'[1]MM-roma5'!S44)/'[1]MM-roma5'!S44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -4258,8 +5373,12 @@
       <c r="X45">
         <v>0.14862513542175201</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="2">
+        <f>(N45-'[1]MM-roma5'!S45)/'[1]MM-roma5'!S45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -4332,8 +5451,12 @@
       <c r="X46">
         <v>0.18639421463012601</v>
       </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="2">
+        <f>(N46-'[1]MM-roma5'!S46)/'[1]MM-roma5'!S46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>68</v>
       </c>
@@ -4406,8 +5529,12 @@
       <c r="X47">
         <v>0.116384983062744</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="2">
+        <f>(N47-'[1]MM-roma5'!S47)/'[1]MM-roma5'!S47</f>
+        <v>1.5781378802067419E-15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>69</v>
       </c>
@@ -4480,8 +5607,12 @@
       <c r="X48">
         <v>0.200875043869018</v>
       </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="2">
+        <f>(N48-'[1]MM-roma5'!S48)/'[1]MM-roma5'!S48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>70</v>
       </c>
@@ -4554,8 +5685,12 @@
       <c r="X49">
         <v>0.19877600669860801</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="2">
+        <f>(N49-'[1]MM-roma5'!S49)/'[1]MM-roma5'!S49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>71</v>
       </c>
@@ -4628,8 +5763,12 @@
       <c r="X50">
         <v>0.180721044540405</v>
       </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="2">
+        <f>(N50-'[1]MM-roma5'!S50)/'[1]MM-roma5'!S50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>72</v>
       </c>
@@ -4701,6 +5840,10 @@
       </c>
       <c r="X51">
         <v>0.24515295028686501</v>
+      </c>
+      <c r="Y51" s="2">
+        <f>(N51-'[1]MM-roma5'!S51)/'[1]MM-roma5'!S51</f>
+        <v>1.5057029745256935E-15</v>
       </c>
     </row>
   </sheetData>
@@ -4710,10 +5853,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782E7FF1-B73E-D449-91EB-F52D4280D94C}">
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -4783,8 +5926,11 @@
       <c r="X1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -4857,8 +6003,12 @@
       <c r="X2">
         <v>1.9626140594482401E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y2" s="3">
+        <f>(N2-'[1]MM-napoli5'!S2)/'[1]MM-napoli5'!S2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -4931,8 +6081,12 @@
       <c r="X3">
         <v>1.5483140945434499E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y3" s="3">
+        <f>(N3-'[1]MM-napoli5'!S3)/'[1]MM-napoli5'!S3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -5005,8 +6159,12 @@
       <c r="X4">
         <v>9.1261863708496094E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y4" s="3">
+        <f>(N4-'[1]MM-napoli5'!S4)/'[1]MM-napoli5'!S4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -5079,8 +6237,12 @@
       <c r="X5">
         <v>1.13928318023681E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y5" s="3">
+        <f>(N5-'[1]MM-napoli5'!S5)/'[1]MM-napoli5'!S5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -5153,8 +6315,12 @@
       <c r="X6">
         <v>1.65600776672363E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y6" s="3">
+        <f>(N6-'[1]MM-napoli5'!S6)/'[1]MM-napoli5'!S6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -5227,8 +6393,12 @@
       <c r="X7">
         <v>1.72188282012939E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="3">
+        <f>(N7-'[1]MM-napoli5'!S7)/'[1]MM-napoli5'!S7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>79</v>
       </c>
@@ -5301,8 +6471,12 @@
       <c r="X8">
         <v>1.56061649322509E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <f>(N8-'[1]MM-napoli5'!S8)/'[1]MM-napoli5'!S8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>80</v>
       </c>
@@ -5375,8 +6549,12 @@
       <c r="X9">
         <v>1.4447927474975499E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3">
+        <f>(N9-'[1]MM-napoli5'!S9)/'[1]MM-napoli5'!S9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>81</v>
       </c>
@@ -5449,8 +6627,12 @@
       <c r="X10">
         <v>1.2315034866332999E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3">
+        <f>(N10-'[1]MM-napoli5'!S10)/'[1]MM-napoli5'!S10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -5523,8 +6705,12 @@
       <c r="X11">
         <v>1.87809467315673E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3">
+        <f>(N11-'[1]MM-napoli5'!S11)/'[1]MM-napoli5'!S11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -5597,8 +6783,12 @@
       <c r="X12">
         <v>3.7317037582397398E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3">
+        <f>(N12-'[1]MM-napoli5'!S12)/'[1]MM-napoli5'!S12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -5671,8 +6861,12 @@
       <c r="X13">
         <v>5.9529066085815402E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <f>(N13-'[1]MM-napoli5'!S13)/'[1]MM-napoli5'!S13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -5745,8 +6939,12 @@
       <c r="X14">
         <v>5.7321071624755797E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <f>(N14-'[1]MM-napoli5'!S14)/'[1]MM-napoli5'!S14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -5819,8 +7017,12 @@
       <c r="X15">
         <v>2.7444839477539E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <f>(N15-'[1]MM-napoli5'!S15)/'[1]MM-napoli5'!S15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -5893,8 +7095,12 @@
       <c r="X16">
         <v>4.4922113418579102E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3">
+        <f>(N16-'[1]MM-napoli5'!S16)/'[1]MM-napoli5'!S16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -5967,8 +7173,12 @@
       <c r="X17">
         <v>2.2231817245483398E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <f>(N17-'[1]MM-napoli5'!S17)/'[1]MM-napoli5'!S17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -6041,8 +7251,12 @@
       <c r="X18">
         <v>6.3560009002685505E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <f>(N18-'[1]MM-napoli5'!S18)/'[1]MM-napoli5'!S18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -6115,8 +7329,12 @@
       <c r="X19">
         <v>3.3818960189819301E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3">
+        <f>(N19-'[1]MM-napoli5'!S19)/'[1]MM-napoli5'!S19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -6189,8 +7407,12 @@
       <c r="X20">
         <v>4.1668891906738198E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <f>(N20-'[1]MM-napoli5'!S20)/'[1]MM-napoli5'!S20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -6263,8 +7485,12 @@
       <c r="X21">
         <v>5.6117057800292899E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3">
+        <f>(N21-'[1]MM-napoli5'!S21)/'[1]MM-napoli5'!S21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -6337,8 +7563,12 @@
       <c r="X22">
         <v>4.14860248565673E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <f>(N22-'[1]MM-napoli5'!S22)/'[1]MM-napoli5'!S22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -6411,8 +7641,12 @@
       <c r="X23">
         <v>5.8081150054931599E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <f>(N23-'[1]MM-napoli5'!S23)/'[1]MM-napoli5'!S23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -6485,8 +7719,12 @@
       <c r="X24">
         <v>7.4579954147338798E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <f>(N24-'[1]MM-napoli5'!S24)/'[1]MM-napoli5'!S24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -6559,8 +7797,12 @@
       <c r="X25">
         <v>0.12897181510925201</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <f>(N25-'[1]MM-napoli5'!S25)/'[1]MM-napoli5'!S25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>97</v>
       </c>
@@ -6633,8 +7875,12 @@
       <c r="X26">
         <v>7.60388374328613E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <f>(N26-'[1]MM-napoli5'!S26)/'[1]MM-napoli5'!S26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -6707,8 +7953,12 @@
       <c r="X27">
         <v>4.3817043304443297E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <f>(N27-'[1]MM-napoli5'!S27)/'[1]MM-napoli5'!S27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>99</v>
       </c>
@@ -6781,8 +8031,12 @@
       <c r="X28">
         <v>8.7725162506103502E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <f>(N28-'[1]MM-napoli5'!S28)/'[1]MM-napoli5'!S28</f>
+        <v>3.4292699930525701E-15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>100</v>
       </c>
@@ -6855,8 +8109,12 @@
       <c r="X29">
         <v>0.12557101249694799</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <f>(N29-'[1]MM-napoli5'!S29)/'[1]MM-napoli5'!S29</f>
+        <v>-2.5398563014190697E-15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -6929,8 +8187,12 @@
       <c r="X30">
         <v>9.0689897537231404E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <f>(N30-'[1]MM-napoli5'!S30)/'[1]MM-napoli5'!S30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -7003,8 +8265,12 @@
       <c r="X31">
         <v>9.8134040832519503E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <f>(N31-'[1]MM-napoli5'!S31)/'[1]MM-napoli5'!S31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -7077,8 +8343,12 @@
       <c r="X32">
         <v>8.1711053848266602E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <f>(N32-'[1]MM-napoli5'!S32)/'[1]MM-napoli5'!S32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -7151,8 +8421,12 @@
       <c r="X33">
         <v>0.154803991317749</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <f>(N33-'[1]MM-napoli5'!S33)/'[1]MM-napoli5'!S33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -7225,8 +8499,12 @@
       <c r="X34">
         <v>0.160907983779907</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <f>(N34-'[1]MM-napoli5'!S34)/'[1]MM-napoli5'!S34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>106</v>
       </c>
@@ -7299,8 +8577,12 @@
       <c r="X35">
         <v>0.16063499450683499</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <f>(N35-'[1]MM-napoli5'!S35)/'[1]MM-napoli5'!S35</f>
+        <v>-2.346516400053241E-15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>107</v>
       </c>
@@ -7373,8 +8655,12 @@
       <c r="X36">
         <v>0.138388156890869</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y36" s="3">
+        <f>(N36-'[1]MM-napoli5'!S36)/'[1]MM-napoli5'!S36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -7447,8 +8733,12 @@
       <c r="X37">
         <v>0.119357109069824</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y37" s="3">
+        <f>(N37-'[1]MM-napoli5'!S37)/'[1]MM-napoli5'!S37</f>
+        <v>2.8710042823699925E-15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>109</v>
       </c>
@@ -7521,8 +8811,12 @@
       <c r="X38">
         <v>0.139452934265136</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="3">
+        <f>(N38-'[1]MM-napoli5'!S38)/'[1]MM-napoli5'!S38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -7595,8 +8889,12 @@
       <c r="X39">
         <v>0.12016797065734799</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3">
+        <f>(N39-'[1]MM-napoli5'!S39)/'[1]MM-napoli5'!S39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>111</v>
       </c>
@@ -7669,8 +8967,12 @@
       <c r="X40">
         <v>0.109158992767333</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3">
+        <f>(N40-'[1]MM-napoli5'!S40)/'[1]MM-napoli5'!S40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>112</v>
       </c>
@@ -7743,8 +9045,12 @@
       <c r="X41">
         <v>0.15090990066528301</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3">
+        <f>(N41-'[1]MM-napoli5'!S41)/'[1]MM-napoli5'!S41</f>
+        <v>-1.3640290583615936E-6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -7817,8 +9123,12 @@
       <c r="X42">
         <v>0.15218305587768499</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <f>(N42-'[1]MM-napoli5'!S42)/'[1]MM-napoli5'!S42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -7891,8 +9201,12 @@
       <c r="X43">
         <v>0.130799055099487</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <f>(N43-'[1]MM-napoli5'!S43)/'[1]MM-napoli5'!S43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>115</v>
       </c>
@@ -7965,8 +9279,12 @@
       <c r="X44">
         <v>0.17360186576843201</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <f>(N44-'[1]MM-napoli5'!S44)/'[1]MM-napoli5'!S44</f>
+        <v>-1.1556833090105243E-5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>116</v>
       </c>
@@ -8039,8 +9357,12 @@
       <c r="X45">
         <v>0.20654797554016099</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <f>(N45-'[1]MM-napoli5'!S45)/'[1]MM-napoli5'!S45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -8113,8 +9435,12 @@
       <c r="X46">
         <v>0.20051193237304599</v>
       </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <f>(N46-'[1]MM-napoli5'!S46)/'[1]MM-napoli5'!S46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -8187,8 +9513,12 @@
       <c r="X47">
         <v>0.171558141708374</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <f>(N47-'[1]MM-napoli5'!S47)/'[1]MM-napoli5'!S47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>119</v>
       </c>
@@ -8261,8 +9591,12 @@
       <c r="X48">
         <v>0.147707939147949</v>
       </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <f>(N48-'[1]MM-napoli5'!S48)/'[1]MM-napoli5'!S48</f>
+        <v>-1.2584629620291411E-6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>120</v>
       </c>
@@ -8335,8 +9669,12 @@
       <c r="X49">
         <v>0.266209125518798</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <f>(N49-'[1]MM-napoli5'!S49)/'[1]MM-napoli5'!S49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>121</v>
       </c>
@@ -8409,8 +9747,12 @@
       <c r="X50">
         <v>0.12687611579895</v>
       </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <f>(N50-'[1]MM-napoli5'!S50)/'[1]MM-napoli5'!S50</f>
+        <v>2.0146723248323805E-15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>122</v>
       </c>
@@ -8482,6 +9824,10 @@
       </c>
       <c r="X51">
         <v>0.10423994064331001</v>
+      </c>
+      <c r="Y51" s="3">
+        <f>(N51-'[1]MM-napoli5'!S51)/'[1]MM-napoli5'!S51</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8491,10 +9837,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBFF563D-91EA-6941-AE4C-B26953F50FF9}">
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -8564,8 +9910,11 @@
       <c r="X1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -8638,8 +9987,12 @@
       <c r="X2">
         <v>2.1567821502685498E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y2" s="3">
+        <f>(N2-'[1]MM-milano5'!S2)/'[1]MM-milano5'!U2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -8712,8 +10065,12 @@
       <c r="X3">
         <v>2.5844097137451099E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y3" s="3">
+        <f>(N3-'[1]MM-milano5'!S3)/'[1]MM-milano5'!U3</f>
+        <v>1.6548503038153682E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>125</v>
       </c>
@@ -8786,8 +10143,12 @@
       <c r="X4">
         <v>1.4283895492553701E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y4" s="3">
+        <f>(N4-'[1]MM-milano5'!S4)/'[1]MM-milano5'!U4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>126</v>
       </c>
@@ -8860,8 +10221,12 @@
       <c r="X5">
         <v>2.6597023010253899E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y5" s="3">
+        <f>(N5-'[1]MM-milano5'!S5)/'[1]MM-milano5'!U5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>127</v>
       </c>
@@ -8934,8 +10299,12 @@
       <c r="X6">
         <v>1.05359554290771E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y6" s="3">
+        <f>(N6-'[1]MM-milano5'!S6)/'[1]MM-milano5'!U6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -9008,8 +10377,12 @@
       <c r="X7">
         <v>1.51238441467285E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="3">
+        <f>(N7-'[1]MM-milano5'!S7)/'[1]MM-milano5'!U7</f>
+        <v>-1.1432079868899915E-15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>129</v>
       </c>
@@ -9082,8 +10455,12 @@
       <c r="X8">
         <v>1.24719142913818E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <f>(N8-'[1]MM-milano5'!S8)/'[1]MM-milano5'!U8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>130</v>
       </c>
@@ -9156,8 +10533,12 @@
       <c r="X9">
         <v>1.8160820007324201E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3">
+        <f>(N9-'[1]MM-milano5'!S9)/'[1]MM-milano5'!U9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>131</v>
       </c>
@@ -9230,8 +10611,12 @@
       <c r="X10">
         <v>3.5557985305786098E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3">
+        <f>(N10-'[1]MM-milano5'!S10)/'[1]MM-milano5'!U10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>132</v>
       </c>
@@ -9304,8 +10689,12 @@
       <c r="X11">
         <v>2.4886846542358398E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3">
+        <f>(N11-'[1]MM-milano5'!S11)/'[1]MM-milano5'!U11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>133</v>
       </c>
@@ -9378,8 +10767,12 @@
       <c r="X12">
         <v>2.1022081375122001E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3">
+        <f>(N12-'[1]MM-milano5'!S12)/'[1]MM-milano5'!U12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>134</v>
       </c>
@@ -9452,8 +10845,12 @@
       <c r="X13">
         <v>5.41739463806152E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <f>(N13-'[1]MM-milano5'!S13)/'[1]MM-milano5'!U13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>135</v>
       </c>
@@ -9526,8 +10923,12 @@
       <c r="X14">
         <v>4.18338775634765E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <f>(N14-'[1]MM-milano5'!S14)/'[1]MM-milano5'!U14</f>
+        <v>3.019600966762676E-15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>136</v>
       </c>
@@ -9600,8 +11001,12 @@
       <c r="X15">
         <v>4.8834800720214802E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <f>(N15-'[1]MM-milano5'!S15)/'[1]MM-milano5'!U15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>137</v>
       </c>
@@ -9674,8 +11079,12 @@
       <c r="X16">
         <v>2.7840852737426699E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3">
+        <f>(N16-'[1]MM-milano5'!S16)/'[1]MM-milano5'!U16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>138</v>
       </c>
@@ -9748,8 +11157,12 @@
       <c r="X17">
         <v>2.9906034469604399E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <f>(N17-'[1]MM-milano5'!S17)/'[1]MM-milano5'!U17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>139</v>
       </c>
@@ -9822,8 +11235,12 @@
       <c r="X18">
         <v>3.6154031753539997E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <f>(N18-'[1]MM-milano5'!S18)/'[1]MM-milano5'!U18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>140</v>
       </c>
@@ -9896,8 +11313,12 @@
       <c r="X19">
         <v>5.6308031082153299E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3">
+        <f>(N19-'[1]MM-milano5'!S19)/'[1]MM-milano5'!U19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>141</v>
       </c>
@@ -9970,8 +11391,12 @@
       <c r="X20">
         <v>1.7186880111694301E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <f>(N20-'[1]MM-milano5'!S20)/'[1]MM-milano5'!U20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>142</v>
       </c>
@@ -10044,8 +11469,12 @@
       <c r="X21">
         <v>6.0053825378417899E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3">
+        <f>(N21-'[1]MM-milano5'!S21)/'[1]MM-milano5'!U21</f>
+        <v>-3.6056795161795E-15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>143</v>
       </c>
@@ -10118,8 +11547,12 @@
       <c r="X22">
         <v>0.101805210113525</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <f>(N22-'[1]MM-milano5'!S22)/'[1]MM-milano5'!U22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>144</v>
       </c>
@@ -10192,8 +11625,12 @@
       <c r="X23">
         <v>5.1162004470825098E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <f>(N23-'[1]MM-milano5'!S23)/'[1]MM-milano5'!U23</f>
+        <v>2.3717682029655461E-15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>145</v>
       </c>
@@ -10266,8 +11703,12 @@
       <c r="X24">
         <v>5.8845996856689398E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <f>(N24-'[1]MM-milano5'!S24)/'[1]MM-milano5'!U24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -10340,8 +11781,12 @@
       <c r="X25">
         <v>8.4918975830078097E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <f>(N25-'[1]MM-milano5'!S25)/'[1]MM-milano5'!U25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>147</v>
       </c>
@@ -10414,8 +11859,12 @@
       <c r="X26">
         <v>4.97488975524902E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <f>(N26-'[1]MM-milano5'!S26)/'[1]MM-milano5'!U26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>148</v>
       </c>
@@ -10488,8 +11937,12 @@
       <c r="X27">
         <v>7.8638076782226493E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <f>(N27-'[1]MM-milano5'!S27)/'[1]MM-milano5'!U27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>149</v>
       </c>
@@ -10562,8 +12015,12 @@
       <c r="X28">
         <v>6.7970991134643499E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <f>(N28-'[1]MM-milano5'!S28)/'[1]MM-milano5'!U28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>150</v>
       </c>
@@ -10636,8 +12093,12 @@
       <c r="X29">
         <v>0.16345810890197701</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <f>(N29-'[1]MM-milano5'!S29)/'[1]MM-milano5'!U29</f>
+        <v>-1.9325172346071155E-15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>151</v>
       </c>
@@ -10710,8 +12171,12 @@
       <c r="X30">
         <v>9.3498945236205999E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <f>(N30-'[1]MM-milano5'!S30)/'[1]MM-milano5'!U30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>152</v>
       </c>
@@ -10784,8 +12249,12 @@
       <c r="X31">
         <v>8.7896108627319294E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <f>(N31-'[1]MM-milano5'!S31)/'[1]MM-milano5'!U31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>153</v>
       </c>
@@ -10858,8 +12327,12 @@
       <c r="X32">
         <v>0.123516082763671</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <f>(N32-'[1]MM-milano5'!S32)/'[1]MM-milano5'!U32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>154</v>
       </c>
@@ -10932,8 +12405,12 @@
       <c r="X33">
         <v>7.57641792297363E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <f>(N33-'[1]MM-milano5'!S33)/'[1]MM-milano5'!U33</f>
+        <v>-2.0564117930534012E-15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>155</v>
       </c>
@@ -11006,8 +12483,12 @@
       <c r="X34">
         <v>0.123351097106933</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <f>(N34-'[1]MM-milano5'!S34)/'[1]MM-milano5'!U34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>156</v>
       </c>
@@ -11080,8 +12561,12 @@
       <c r="X35">
         <v>8.8108062744140597E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <f>(N35-'[1]MM-milano5'!S35)/'[1]MM-milano5'!U35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -11154,8 +12639,12 @@
       <c r="X36">
         <v>0.14210486412048301</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y36" s="3">
+        <f>(N36-'[1]MM-milano5'!S36)/'[1]MM-milano5'!U36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>158</v>
       </c>
@@ -11228,8 +12717,12 @@
       <c r="X37">
         <v>0.123531103134155</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y37" s="3">
+        <f>(N37-'[1]MM-milano5'!S37)/'[1]MM-milano5'!U37</f>
+        <v>2.16254818946098E-15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>159</v>
       </c>
@@ -11302,8 +12795,12 @@
       <c r="X38">
         <v>0.12473416328430099</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="3">
+        <f>(N38-'[1]MM-milano5'!S38)/'[1]MM-milano5'!U38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>160</v>
       </c>
@@ -11376,8 +12873,12 @@
       <c r="X39">
         <v>0.14569091796875</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3">
+        <f>(N39-'[1]MM-milano5'!S39)/'[1]MM-milano5'!U39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>161</v>
       </c>
@@ -11450,8 +12951,12 @@
       <c r="X40">
         <v>9.3567132949829102E-2</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3">
+        <f>(N40-'[1]MM-milano5'!S40)/'[1]MM-milano5'!U40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>162</v>
       </c>
@@ -11524,8 +13029,12 @@
       <c r="X41">
         <v>7.46738910675048E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3">
+        <f>(N41-'[1]MM-milano5'!S41)/'[1]MM-milano5'!U41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>163</v>
       </c>
@@ -11598,8 +13107,12 @@
       <c r="X42">
         <v>0.113881111145019</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <f>(N42-'[1]MM-milano5'!S42)/'[1]MM-milano5'!U42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>164</v>
       </c>
@@ -11672,8 +13185,12 @@
       <c r="X43">
         <v>0.15764498710632299</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <f>(N43-'[1]MM-milano5'!S43)/'[1]MM-milano5'!U43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>165</v>
       </c>
@@ -11746,8 +13263,12 @@
       <c r="X44">
         <v>0.190943002700805</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <f>(N44-'[1]MM-milano5'!S44)/'[1]MM-milano5'!U44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>166</v>
       </c>
@@ -11820,8 +13341,12 @@
       <c r="X45">
         <v>0.21588301658630299</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <f>(N45-'[1]MM-milano5'!S45)/'[1]MM-milano5'!U45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>167</v>
       </c>
@@ -11894,8 +13419,12 @@
       <c r="X46">
         <v>0.173687934875488</v>
       </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <f>(N46-'[1]MM-milano5'!S46)/'[1]MM-milano5'!U46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>168</v>
       </c>
@@ -11968,8 +13497,12 @@
       <c r="X47">
         <v>0.104106187820434</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <f>(N47-'[1]MM-milano5'!S47)/'[1]MM-milano5'!U47</f>
+        <v>1.6686794531312538E-15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>169</v>
       </c>
@@ -12042,8 +13575,12 @@
       <c r="X48">
         <v>0.19507884979248</v>
       </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <f>(N48-'[1]MM-milano5'!S48)/'[1]MM-milano5'!U48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>170</v>
       </c>
@@ -12116,8 +13653,12 @@
       <c r="X49">
         <v>0.22132396697998</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <f>(N49-'[1]MM-milano5'!S49)/'[1]MM-milano5'!U49</f>
+        <v>-1.3157108514409983E-15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>171</v>
       </c>
@@ -12190,8 +13731,12 @@
       <c r="X50">
         <v>0.295459985733032</v>
       </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <f>(N50-'[1]MM-milano5'!S50)/'[1]MM-milano5'!U50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>172</v>
       </c>
@@ -12263,6 +13808,10 @@
       </c>
       <c r="X51">
         <v>0.29196810722351002</v>
+      </c>
+      <c r="Y51" s="3">
+        <f>(N51-'[1]MM-milano5'!S51)/'[1]MM-milano5'!U51</f>
+        <v>1.3446108600856721E-15</v>
       </c>
     </row>
   </sheetData>
